--- a/Config/Datas/player_status.xlsx
+++ b/Config/Datas/player_status.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="player_desire_level" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="player_" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>##var</t>
   </si>
@@ -43,12 +43,21 @@
     <t>basic_estrus</t>
   </si>
   <si>
+    <t>aura_base_effect</t>
+  </si>
+  <si>
+    <t>aura_max_range</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -65,6 +74,9 @@
   </si>
   <si>
     <t>基准发情</t>
+  </si>
+  <si>
+    <t>每秒传播</t>
   </si>
 </sst>
 </file>
@@ -996,13 +1008,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="12.75" customWidth="1"/>
+    <col min="4" max="4" width="11.75" customWidth="1"/>
+    <col min="5" max="5" width="11.25" customWidth="1"/>
+    <col min="6" max="6" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1015,50 +1030,74 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:6">
       <c r="B5">
         <v>0</v>
       </c>
@@ -1068,8 +1107,11 @@
       <c r="D5">
         <v>0</v>
       </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:6">
       <c r="B6">
         <v>1</v>
       </c>
@@ -1079,8 +1121,14 @@
       <c r="D6">
         <v>20</v>
       </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:6">
       <c r="B7">
         <v>2</v>
       </c>
@@ -1090,8 +1138,14 @@
       <c r="D7">
         <v>40</v>
       </c>
+      <c r="E7">
+        <v>1.5</v>
+      </c>
+      <c r="F7">
+        <v>1.3</v>
+      </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6">
       <c r="B8" s="1">
         <v>3</v>
       </c>
@@ -1101,8 +1155,14 @@
       <c r="D8">
         <v>60</v>
       </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>1.6</v>
+      </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6">
       <c r="B9">
         <v>4</v>
       </c>
@@ -1111,6 +1171,12 @@
       </c>
       <c r="D9">
         <v>90</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/player_status.xlsx
+++ b/Config/Datas/player_status.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="player_desire_level" sheetId="1" r:id="rId1"/>
@@ -1102,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>999</v>
+        <v>75</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1116,7 +1116,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D6">
         <v>20</v>
@@ -1133,7 +1133,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D7">
         <v>40</v>
@@ -1150,7 +1150,7 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>60</v>
@@ -1167,7 +1167,7 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>90</v>

--- a/Config/Datas/player_status.xlsx
+++ b/Config/Datas/player_status.xlsx
@@ -1,250 +1,180 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="player_desire_level" sheetId="1" r:id="rId1"/>
-    <sheet name="player_" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="player_desire_level" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="player_" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="spirit_monster_budget" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>san_line</t>
-  </si>
-  <si>
-    <t>basic_estrus</t>
-  </si>
-  <si>
-    <t>aura_base_effect</t>
-  </si>
-  <si>
-    <t>aura_max_range</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c,s</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>等级</t>
-  </si>
-  <si>
-    <t>理智线</t>
-  </si>
-  <si>
-    <t>基准发情</t>
-  </si>
-  <si>
-    <t>每秒传播</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -544,159 +474,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -750,11 +680,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1006,206 +999,705 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="12.75" customWidth="1"/>
-    <col min="4" max="4" width="11.75" customWidth="1"/>
-    <col min="5" max="5" width="11.25" customWidth="1"/>
-    <col min="6" max="6" width="12.125" customWidth="1"/>
+    <col width="12.75" customWidth="1" style="1" min="3" max="3"/>
+    <col width="11.75" customWidth="1" style="1" min="4" max="4"/>
+    <col width="11.25" customWidth="1" style="1" min="5" max="5"/>
+    <col width="12.125" customWidth="1" style="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>san_line</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>basic_estrus</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>aura_base_effect</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>aura_max_range</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>spirit_monster_total_budget</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>spirit_monster_refresh_interval_sec</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>ambient_spirit_count</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>ambient_spirit_radius_min</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>ambient_spirit_radius_max</t>
+        </is>
+      </c>
+      <c r="L1" s="0" t="inlineStr">
+        <is>
+          <t>ambient_spirit_prefab</t>
+        </is>
+      </c>
+      <c r="M1" s="0" t="inlineStr">
+        <is>
+          <t>ambient_spirit_drift_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="K3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>理智线</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>基准发情</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>每秒传播</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>每秒传播</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>实战影怪总预算(各类型 budget_cost 之和上限)</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>按预算补全影怪的刷新间隔(秒)</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>后场氛围假影怪数量</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
+          <t>后场环绕最小半径</t>
+        </is>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t>后场环绕最大半径</t>
+        </is>
+      </c>
+      <c r="L4" s="0" t="inlineStr">
+        <is>
+          <t>Resources路径(无扩展名), 空则不生成</t>
+        </is>
+      </c>
+      <c r="M4" s="0" t="inlineStr">
+        <is>
+          <t>后场漂移速度系数</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C5" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" s="0" t="inlineStr"/>
+      <c r="M5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="6">
+      <c r="B6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="L6" s="0" t="inlineStr"/>
+      <c r="M6" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C7" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" s="0" t="inlineStr"/>
+      <c r="M7" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C8" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="L8" s="0" t="inlineStr"/>
+      <c r="M8" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="C9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" s="0" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="J9" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>75</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>50</v>
-      </c>
-      <c r="D6">
-        <v>20</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>35</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>1.5</v>
-      </c>
-      <c r="F7">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>60</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>90</v>
-      </c>
-      <c r="E9">
-        <v>3</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
+      <c r="K9" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="L9" s="0" t="inlineStr"/>
+      <c r="M9" s="0" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>npc_cfg_id</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>budget_cost</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>min_desire_level</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>restore_san</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>spawn_weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>row id</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>TbUnitNpc id</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>budget cost per spawn</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>min desire level</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>restore sanity on kill</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>spawn weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>h_spirit_small_01_d3</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>h_spirit_small_01</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>h_spirit_small_02_d4</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>h_spirit_small_02</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Config/Datas/player_status.xlsx
+++ b/Config/Datas/player_status.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="3"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="player_desire_level" sheetId="1" r:id="rId1"/>
@@ -1115,6 +1115,7 @@
     <col min="4" max="4" width="11.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1339,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1377,7 +1378,7 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1415,7 +1416,7 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>7</v>
@@ -1453,7 +1454,7 @@
         <v>6</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>8</v>

--- a/Config/Datas/player_status.xlsx
+++ b/Config/Datas/player_status.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="player_desire_level" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -131,7 +131,7 @@
     <t>id</t>
   </si>
   <si>
-    <t>npc_cfg_id</t>
+    <t>npc_base_type</t>
   </si>
   <si>
     <t>budget_cost</t>
@@ -167,16 +167,7 @@
     <t>spawn weight</t>
   </si>
   <si>
-    <t>h_spirit_small_01_d3</t>
-  </si>
-  <si>
-    <t>h_spirit_small_01</t>
-  </si>
-  <si>
-    <t>h_spirit_small_02_d4</t>
-  </si>
-  <si>
-    <t>h_spirit_small_02</t>
+    <t>h_spirit_small</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1106,10 @@
     <col min="4" max="4" width="11.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.875" customWidth="1"/>
+    <col min="8" max="8" width="11.5" customWidth="1"/>
+    <col min="9" max="9" width="20.5" customWidth="1"/>
+    <col min="10" max="10" width="17.25" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1503,8 +1497,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="2" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="11.125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
@@ -1599,17 +1598,17 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="B5" t="s">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
         <v>45</v>
-      </c>
-      <c r="C5" t="s">
-        <v>46</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>5000</v>
@@ -1619,22 +1618,62 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="B6" t="s">
-        <v>47</v>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>5000</v>
       </c>
       <c r="G6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>5000</v>
+      </c>
+      <c r="G7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>5000</v>
+      </c>
+      <c r="G8">
         <v>100</v>
       </c>
     </row>

--- a/Config/Datas/player_status.xlsx
+++ b/Config/Datas/player_status.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="3"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="player_desire_level" sheetId="1" r:id="rId1"/>
-    <sheet name="player_" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="player_jingyu_level" sheetId="2" r:id="rId2"/>
+    <sheet name="player_san_level" sheetId="3" r:id="rId3"/>
     <sheet name="spirit_monster_budget" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -38,112 +38,100 @@
     <t>level</t>
   </si>
   <si>
+    <t>desire_line</t>
+  </si>
+  <si>
+    <t>aura_h_effect</t>
+  </si>
+  <si>
+    <t>aura_max_range</t>
+  </si>
+  <si>
+    <t>spirit_monster_total_budget</t>
+  </si>
+  <si>
+    <t>spirit_monster_refresh_interval_sec</t>
+  </si>
+  <si>
+    <t>ambient_spirit_drift_speed</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c,s</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
+    <t>理智线</t>
+  </si>
+  <si>
+    <t>光环值</t>
+  </si>
+  <si>
+    <t>每秒传播</t>
+  </si>
+  <si>
+    <t>实战影怪总预算(各类型 budget_cost 之和上限)</t>
+  </si>
+  <si>
+    <t>按预算补全影怪的刷新间隔(秒)</t>
+  </si>
+  <si>
+    <t>后场漂移速度系数</t>
+  </si>
+  <si>
+    <t>need_amount</t>
+  </si>
+  <si>
+    <t>estrus_up</t>
+  </si>
+  <si>
+    <t>每秒发情</t>
+  </si>
+  <si>
     <t>san_line</t>
   </si>
   <si>
     <t>basic_estrus</t>
   </si>
   <si>
-    <t>aura_base_effect</t>
-  </si>
-  <si>
-    <t>aura_max_range</t>
-  </si>
-  <si>
-    <t>spirit_monster_total_budget</t>
-  </si>
-  <si>
-    <t>spirit_monster_refresh_interval_sec</t>
-  </si>
-  <si>
-    <t>ambient_spirit_count</t>
-  </si>
-  <si>
-    <t>ambient_spirit_radius_min</t>
-  </si>
-  <si>
-    <t>ambient_spirit_radius_max</t>
-  </si>
-  <si>
-    <t>ambient_spirit_prefab</t>
-  </si>
-  <si>
-    <t>ambient_spirit_drift_speed</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>float</t>
+    <t>基准发情</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>npc_base_type</t>
+  </si>
+  <si>
+    <t>budget_cost</t>
+  </si>
+  <si>
+    <t>min_desire_level</t>
+  </si>
+  <si>
+    <t>restore_san</t>
+  </si>
+  <si>
+    <t>spawn_weight</t>
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c,s</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>等级</t>
-  </si>
-  <si>
-    <t>理智线</t>
-  </si>
-  <si>
-    <t>基准发情</t>
-  </si>
-  <si>
-    <t>每秒传播</t>
-  </si>
-  <si>
-    <t>实战影怪总预算(各类型 budget_cost 之和上限)</t>
-  </si>
-  <si>
-    <t>按预算补全影怪的刷新间隔(秒)</t>
-  </si>
-  <si>
-    <t>后场氛围假影怪数量</t>
-  </si>
-  <si>
-    <t>后场环绕最小半径</t>
-  </si>
-  <si>
-    <t>后场环绕最大半径</t>
-  </si>
-  <si>
-    <t>Resources路径(无扩展名), 空则不生成</t>
-  </si>
-  <si>
-    <t>后场漂移速度系数</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>npc_base_type</t>
-  </si>
-  <si>
-    <t>budget_cost</t>
-  </si>
-  <si>
-    <t>min_desire_level</t>
-  </si>
-  <si>
-    <t>restore_san</t>
-  </si>
-  <si>
-    <t>spawn_weight</t>
   </si>
   <si>
     <t>long</t>
@@ -1099,20 +1087,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="12.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="20.5" customWidth="1"/>
-    <col min="10" max="10" width="17.25" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="12.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1137,154 +1122,97 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>75</v>
-      </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1293,173 +1221,75 @@
         <v>0</v>
       </c>
       <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>40</v>
+      </c>
+      <c r="D6">
+        <v>1.5</v>
+      </c>
+      <c r="E6">
+        <v>1.3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>70</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1.6</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
         <v>8</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>12</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5">
+      <c r="H7">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>50</v>
-      </c>
-      <c r="D6">
-        <v>20</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
+    <row r="8" spans="1:8">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8">
         <v>3</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>35</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>1.5</v>
-      </c>
-      <c r="F7">
-        <v>1.3</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>12</v>
-      </c>
-      <c r="L7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>60</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>6</v>
       </c>
       <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>8</v>
-      </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>90</v>
-      </c>
-      <c r="E9">
-        <v>3</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>6</v>
-      </c>
-      <c r="I9">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <v>8</v>
-      </c>
-      <c r="K9">
-        <v>16</v>
-      </c>
-      <c r="L9" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9">
         <v>1.2</v>
       </c>
     </row>
@@ -1473,9 +1303,124 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>50</v>
+      </c>
+      <c r="D6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>200</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>500</v>
+      </c>
+      <c r="D8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1485,9 +1430,114 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="3" width="10.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>75</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>50</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1500,9 +1550,9 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="18.125" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="11.125" customWidth="1"/>
+    <col min="2" max="2" width="18.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1510,91 +1560,91 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" t="s">
         <v>32</v>
-      </c>
-      <c r="C1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" t="s">
         <v>39</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4" t="s">
         <v>40</v>
-      </c>
-      <c r="D4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1602,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1622,7 +1672,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1642,7 +1692,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1662,7 +1712,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D8">
         <v>3</v>

--- a/Config/Datas/player_status.xlsx
+++ b/Config/Datas/player_status.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="player_desire_level" sheetId="1" r:id="rId1"/>
     <sheet name="player_jingyu_level" sheetId="2" r:id="rId2"/>
-    <sheet name="player_san_level" sheetId="3" r:id="rId3"/>
+    <sheet name="player_san_corrupt_level" sheetId="3" r:id="rId3"/>
     <sheet name="spirit_monster_budget" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -77,31 +77,49 @@
     <t>等级</t>
   </si>
   <si>
+    <t>欲望线</t>
+  </si>
+  <si>
+    <t>光环值</t>
+  </si>
+  <si>
+    <t>每秒传播</t>
+  </si>
+  <si>
+    <t>实战影怪总预算(各类型 budget_cost 之和上限)</t>
+  </si>
+  <si>
+    <t>按预算补全影怪的刷新间隔(秒)</t>
+  </si>
+  <si>
+    <t>后场漂移速度系数</t>
+  </si>
+  <si>
+    <t>need_amount</t>
+  </si>
+  <si>
+    <t>estrus_up</t>
+  </si>
+  <si>
+    <t>cost_per_sec</t>
+  </si>
+  <si>
+    <t>hunger_per_sec</t>
+  </si>
+  <si>
+    <t>hp_per_sec</t>
+  </si>
+  <si>
     <t>理智线</t>
   </si>
   <si>
-    <t>光环值</t>
-  </si>
-  <si>
-    <t>每秒传播</t>
-  </si>
-  <si>
-    <t>实战影怪总预算(各类型 budget_cost 之和上限)</t>
-  </si>
-  <si>
-    <t>按预算补全影怪的刷新间隔(秒)</t>
-  </si>
-  <si>
-    <t>后场漂移速度系数</t>
-  </si>
-  <si>
-    <t>need_amount</t>
-  </si>
-  <si>
-    <t>estrus_up</t>
-  </si>
-  <si>
     <t>每秒发情</t>
+  </si>
+  <si>
+    <t>每秒消耗</t>
+  </si>
+  <si>
+    <t>每秒回饱腹</t>
   </si>
   <si>
     <t>san_line</t>
@@ -1275,7 +1293,7 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -1303,13 +1321,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.125" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1322,8 +1342,17 @@
       <c r="D1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1336,8 +1365,17 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1350,8 +1388,17 @@
       <c r="D3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1359,13 +1406,22 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="B5">
         <v>0</v>
       </c>
@@ -1376,7 +1432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:7">
       <c r="B6">
         <v>1</v>
       </c>
@@ -1386,8 +1442,17 @@
       <c r="D6">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0.5</v>
+      </c>
+      <c r="G6">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7">
         <v>2</v>
       </c>
@@ -1397,8 +1462,17 @@
       <c r="D7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8">
         <v>3</v>
       </c>
@@ -1408,8 +1482,17 @@
       <c r="D8">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>1.5</v>
+      </c>
+      <c r="G8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="B9">
         <v>4</v>
       </c>
@@ -1418,6 +1501,15 @@
       </c>
       <c r="D9">
         <v>2</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1445,10 +1537,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1487,10 +1579,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1560,22 +1652,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1583,10 +1675,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -1595,7 +1687,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
@@ -1629,22 +1721,22 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1652,7 +1744,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1672,7 +1764,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1692,7 +1784,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1712,7 +1804,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D8">
         <v>3</v>

--- a/Config/Datas/player_status.xlsx
+++ b/Config/Datas/player_status.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="player_desire_level" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -41,12 +41,93 @@
     <t>desire_line</t>
   </si>
   <si>
+    <t>extra_charm</t>
+  </si>
+  <si>
+    <t>extra_damage_reduce</t>
+  </si>
+  <si>
+    <t>h_collide_rate</t>
+  </si>
+  <si>
     <t>aura_h_effect</t>
   </si>
   <si>
     <t>aura_max_range</t>
   </si>
   <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c,s</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
+    <t>欲望线</t>
+  </si>
+  <si>
+    <t>额外魅力</t>
+  </si>
+  <si>
+    <t>额外免伤</t>
+  </si>
+  <si>
+    <t>h碰撞千分比</t>
+  </si>
+  <si>
+    <t>光环值</t>
+  </si>
+  <si>
+    <t>每秒传播</t>
+  </si>
+  <si>
+    <t>need_amount</t>
+  </si>
+  <si>
+    <t>estrus_up</t>
+  </si>
+  <si>
+    <t>cost_per_sec</t>
+  </si>
+  <si>
+    <t>hunger_per_sec</t>
+  </si>
+  <si>
+    <t>hp_per_sec</t>
+  </si>
+  <si>
+    <t>理智线</t>
+  </si>
+  <si>
+    <t>每秒发情</t>
+  </si>
+  <si>
+    <t>每秒消耗</t>
+  </si>
+  <si>
+    <t>每秒回饱腹</t>
+  </si>
+  <si>
+    <t>san_line</t>
+  </si>
+  <si>
+    <t>basic_estrus</t>
+  </si>
+  <si>
     <t>spirit_monster_total_budget</t>
   </si>
   <si>
@@ -56,34 +137,7 @@
     <t>ambient_spirit_drift_speed</t>
   </si>
   <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c,s</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>等级</t>
-  </si>
-  <si>
-    <t>欲望线</t>
-  </si>
-  <si>
-    <t>光环值</t>
-  </si>
-  <si>
-    <t>每秒传播</t>
+    <t>基准发情</t>
   </si>
   <si>
     <t>实战影怪总预算(各类型 budget_cost 之和上限)</t>
@@ -95,42 +149,6 @@
     <t>后场漂移速度系数</t>
   </si>
   <si>
-    <t>need_amount</t>
-  </si>
-  <si>
-    <t>estrus_up</t>
-  </si>
-  <si>
-    <t>cost_per_sec</t>
-  </si>
-  <si>
-    <t>hunger_per_sec</t>
-  </si>
-  <si>
-    <t>hp_per_sec</t>
-  </si>
-  <si>
-    <t>理智线</t>
-  </si>
-  <si>
-    <t>每秒发情</t>
-  </si>
-  <si>
-    <t>每秒消耗</t>
-  </si>
-  <si>
-    <t>每秒回饱腹</t>
-  </si>
-  <si>
-    <t>san_line</t>
-  </si>
-  <si>
-    <t>basic_estrus</t>
-  </si>
-  <si>
-    <t>基准发情</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -140,7 +158,7 @@
     <t>budget_cost</t>
   </si>
   <si>
-    <t>min_desire_level</t>
+    <t>min_san_corrupt_level</t>
   </si>
   <si>
     <t>restore_san</t>
@@ -1108,11 +1126,9 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
-    <col min="3" max="3" width="12.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.5" style="1" customWidth="1"/>
+    <col min="3" max="6" width="12.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1155,7 +1171,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -1227,16 +1243,16 @@
         <v>15</v>
       </c>
       <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>2000</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
         <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1250,19 +1266,19 @@
         <v>40</v>
       </c>
       <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>3500</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
         <v>1.5</v>
       </c>
-      <c r="E6">
+      <c r="H6">
         <v>1.3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>12</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1273,19 +1289,19 @@
         <v>70</v>
       </c>
       <c r="D7">
+        <v>50</v>
+      </c>
+      <c r="E7">
+        <v>5000</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
+      </c>
+      <c r="G7">
         <v>2</v>
       </c>
-      <c r="E7">
+      <c r="H7">
         <v>1.6</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1293,22 +1309,22 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="D8">
+        <v>100</v>
+      </c>
+      <c r="E8">
+        <v>9000</v>
+      </c>
+      <c r="F8">
+        <v>50</v>
+      </c>
+      <c r="G8">
         <v>3</v>
       </c>
-      <c r="E8">
+      <c r="H8">
         <v>2</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -1522,14 +1538,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="3" width="10.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1542,8 +1561,17 @@
       <c r="D1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1556,8 +1584,17 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1570,8 +1607,17 @@
       <c r="D3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1582,10 +1628,19 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="B5">
         <v>0</v>
       </c>
@@ -1595,8 +1650,17 @@
       <c r="D5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="B6">
         <v>1</v>
       </c>
@@ -1606,8 +1670,17 @@
       <c r="D6">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7">
         <v>2</v>
       </c>
@@ -1617,8 +1690,17 @@
       <c r="D7">
         <v>70</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8">
         <v>3</v>
       </c>
@@ -1627,6 +1709,15 @@
       </c>
       <c r="D8">
         <v>100</v>
+      </c>
+      <c r="E8">
+        <v>9</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -1652,22 +1743,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1675,10 +1766,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -1687,7 +1778,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
@@ -1721,22 +1812,22 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1744,7 +1835,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1764,7 +1855,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1784,7 +1875,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1804,7 +1895,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D8">
         <v>3</v>

--- a/Config/Datas/player_status.xlsx
+++ b/Config/Datas/player_status.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="player_desire_level" sheetId="1" r:id="rId1"/>

--- a/Config/Datas/player_status.xlsx
+++ b/Config/Datas/player_status.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="2"/>
+    <workbookView windowHeight="17655" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="player_desire_level" sheetId="1" r:id="rId1"/>
     <sheet name="player_jingyu_level" sheetId="2" r:id="rId2"/>
     <sheet name="player_san_corrupt_level" sheetId="3" r:id="rId3"/>
-    <sheet name="spirit_monster_budget" sheetId="4" r:id="rId4"/>
+    <sheet name="player_clothes_expose_info" sheetId="5" r:id="rId4"/>
+    <sheet name="spirit_monster_budget" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -149,6 +150,42 @@
     <t>后场漂移速度系数</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>line_min</t>
+  </si>
+  <si>
+    <t>line_max</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>衣装线min</t>
+  </si>
+  <si>
+    <t>衣装线max</t>
+  </si>
+  <si>
+    <t>完好</t>
+  </si>
+  <si>
+    <t>破损</t>
+  </si>
+  <si>
+    <t>半裸</t>
+  </si>
+  <si>
+    <t>全裸</t>
+  </si>
+  <si>
+    <t>真身</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -165,9 +202,6 @@
   </si>
   <si>
     <t>spawn_weight</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
   <si>
     <t>long</t>
@@ -1730,6 +1764,156 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5">
+        <v>80</v>
+      </c>
+      <c r="E5">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6">
+        <v>50</v>
+      </c>
+      <c r="E6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
@@ -1743,22 +1927,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G1" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1766,10 +1950,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -1778,7 +1962,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
@@ -1812,22 +1996,22 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1835,7 +2019,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1855,7 +2039,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1875,7 +2059,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1895,7 +2079,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D8">
         <v>3</v>

--- a/Config/Datas/player_status.xlsx
+++ b/Config/Datas/player_status.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="3"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="player_desire_level" sheetId="1" r:id="rId1"/>
@@ -1283,7 +1283,7 @@
         <v>2000</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1306,7 +1306,7 @@
         <v>3500</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>1.5</v>
@@ -1329,7 +1329,7 @@
         <v>5000</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1352,7 +1352,7 @@
         <v>9000</v>
       </c>
       <c r="F8">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G8">
         <v>3</v>

--- a/Config/Datas/player_status.xlsx
+++ b/Config/Datas/player_status.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="player_desire_level" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -159,6 +159,12 @@
     <t>line_max</t>
   </si>
   <si>
+    <t>h_impluse_resist</t>
+  </si>
+  <si>
+    <t>gaze_resist</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -169,6 +175,12 @@
   </si>
   <si>
     <t>衣装线max</t>
+  </si>
+  <si>
+    <t>h冲击减伤率</t>
+  </si>
+  <si>
+    <t>视线减伤率</t>
   </si>
   <si>
     <t>完好</t>
@@ -1764,10 +1776,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <cols>
+    <col min="5" max="5" width="10.5" customWidth="1"/>
+    <col min="6" max="6" width="18.25" customWidth="1"/>
+    <col min="7" max="7" width="12.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1783,8 +1800,14 @@
       <c r="E1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1792,7 +1815,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -1800,8 +1823,14 @@
       <c r="E2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1817,8 +1846,14 @@
       <c r="E3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1826,21 +1861,27 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D5">
         <v>80</v>
@@ -1848,13 +1889,19 @@
       <c r="E5">
         <v>999</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5">
+        <v>0.5</v>
+      </c>
+      <c r="G5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D6">
         <v>50</v>
@@ -1862,13 +1909,19 @@
       <c r="E6">
         <v>80</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6">
+        <v>0.25</v>
+      </c>
+      <c r="G6">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D7">
         <v>30</v>
@@ -1876,13 +1929,19 @@
       <c r="E7">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D8">
         <v>10</v>
@@ -1890,19 +1949,31 @@
       <c r="E8">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
         <v>10</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1927,22 +1998,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1950,10 +2021,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -1962,7 +2033,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
@@ -1996,22 +2067,22 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2019,7 +2090,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -2039,7 +2110,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -2059,7 +2130,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -2079,7 +2150,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>3</v>
